--- a/tables/output/TableS16.xlsx
+++ b/tables/output/TableS16.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">group</t>
   </si>
@@ -47,169 +47,52 @@
     <t xml:space="preserve">Event-free survival</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42984257357974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.724161533196441</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIPG or DMG</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38466803559206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620123203285421</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ependymoma</t>
   </si>
   <si>
-    <t xml:space="preserve">Not reached</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05270362765229</t>
-  </si>
-  <si>
     <t xml:space="preserve">GNG/GNT, Other alteration</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9678302532512</t>
-  </si>
-  <si>
     <t xml:space="preserve">HGG, H3 WT</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706365503080082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3223819301848</t>
-  </si>
-  <si>
     <t xml:space="preserve">High-grade glioma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27857631759069</t>
-  </si>
-  <si>
     <t xml:space="preserve">LGG, BRAF V600E</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67830253251198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10403832991102</t>
-  </si>
-  <si>
     <t xml:space="preserve">LGG, BRAF fusion</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75359342915811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3100616016427</t>
-  </si>
-  <si>
     <t xml:space="preserve">LGG, Other alteration</t>
   </si>
   <si>
-    <t xml:space="preserve">10.507871321013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9596167008898</t>
-  </si>
-  <si>
     <t xml:space="preserve">Low-grade glioma</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99931553730322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56331279945243</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB, Group3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24298425735797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603696098562628</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB, Group4</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53593429158111</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB, SHH</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85420944558522</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medulloblastoma</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92881587953457</t>
-  </si>
-  <si>
     <t xml:space="preserve">Meningioma</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11498973305955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64476386036961</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mixed neuronal-glial tumor</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99863107460643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53114305270363</t>
-  </si>
-  <si>
     <t xml:space="preserve">Overall survival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10746064339493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84120465434634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18685831622177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892539356605065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614647501711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57426420260096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42231348391513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34086242299795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5735797399042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1854893908282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12867898699521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09787816563997</t>
   </si>
 </sst>
 </file>
@@ -577,11 +460,11 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
+      <c r="D2" t="n">
+        <v>0.42984257357974</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.724161533196441</v>
       </c>
       <c r="F2" t="n">
         <v>2.13272451106791</v>
@@ -598,7 +481,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>28</v>
@@ -606,11 +489,11 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
+      <c r="D3" t="n">
+        <v>0.38466803559206</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.620123203285421</v>
       </c>
       <c r="F3" t="n">
         <v>0.892087899745178</v>
@@ -627,7 +510,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>58</v>
@@ -635,11 +518,11 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
+      <c r="D4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.05270362765229</v>
       </c>
       <c r="F4" t="n">
         <v>0.166727417854626</v>
@@ -656,7 +539,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>31</v>
@@ -664,11 +547,11 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
+      <c r="D5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.9678302532512</v>
       </c>
       <c r="F5" t="n">
         <v>5.57831632469752</v>
@@ -685,7 +568,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>31</v>
@@ -693,11 +576,11 @@
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
+      <c r="D6" t="n">
+        <v>0.706365503080082</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.3223819301848</v>
       </c>
       <c r="F6" t="n">
         <v>0.875403158046352</v>
@@ -714,7 +597,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>39</v>
@@ -722,11 +605,11 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
+      <c r="D7" t="n">
+        <v>0.706365503080082</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.27857631759069</v>
       </c>
       <c r="F7" t="n">
         <v>0.879730208400027</v>
@@ -743,7 +626,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>24</v>
@@ -751,11 +634,11 @@
       <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
+      <c r="D8" t="n">
+        <v>1.67830253251198</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.10403832991102</v>
       </c>
       <c r="F8" t="n">
         <v>1.27991858356653</v>
@@ -772,7 +655,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>87</v>
@@ -780,11 +663,11 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+      <c r="D9" t="n">
+        <v>3.75359342915811</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11.3100616016427</v>
       </c>
       <c r="F9" t="n">
         <v>2.67431168701208</v>
@@ -801,7 +684,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>44</v>
@@ -809,11 +692,11 @@
       <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
+      <c r="D10" t="n">
+        <v>10.507871321013</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.9596167008898</v>
       </c>
       <c r="F10" t="n">
         <v>0.632120738740167</v>
@@ -830,7 +713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>177</v>
@@ -838,11 +721,11 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
+      <c r="D11" t="n">
+        <v>4.99931553730322</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.56331279945243</v>
       </c>
       <c r="F11" t="n">
         <v>1.09959092583813</v>
@@ -859,7 +742,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>19</v>
@@ -867,11 +750,11 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
+      <c r="D12" t="n">
+        <v>1.24298425735797</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.603696098562628</v>
       </c>
       <c r="F12" t="n">
         <v>0.523214204273428</v>
@@ -888,7 +771,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>39</v>
@@ -896,11 +779,11 @@
       <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.53593429158111</v>
       </c>
       <c r="F13" t="n">
         <v>0.14799876740403</v>
@@ -917,7 +800,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>16</v>
@@ -925,11 +808,11 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
+      <c r="D14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.85420944558522</v>
       </c>
       <c r="F14" t="n">
         <v>0.079643296689479</v>
@@ -946,7 +829,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>83</v>
@@ -954,11 +837,11 @@
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="s">
-        <v>46</v>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.92881587953457</v>
       </c>
       <c r="F15" t="n">
         <v>0.232915022608329</v>
@@ -975,7 +858,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
         <v>22</v>
@@ -983,11 +866,11 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
+      <c r="D16" t="n">
+        <v>4.11498973305955</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.64476386036961</v>
       </c>
       <c r="F16" t="n">
         <v>0.278962701033817</v>
@@ -1004,7 +887,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B17" t="n">
         <v>57</v>
@@ -1012,11 +895,11 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
+      <c r="D17" t="n">
+        <v>1.99863107460643</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.53114305270363</v>
       </c>
       <c r="F17" t="n">
         <v>3.50133190126108</v>
@@ -1039,13 +922,13 @@
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.10746064339493</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.84120465434634</v>
       </c>
       <c r="F18" t="n">
         <v>0.717685598287816</v>
@@ -1062,19 +945,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
         <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
+        <v>26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.18685831622177</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.892539356605065</v>
       </c>
       <c r="F19" t="n">
         <v>0.570172611545256</v>
@@ -1091,19 +974,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B20" t="n">
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10.2614647501711</v>
+      </c>
+      <c r="E20" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F20" t="n">
         <v>0.570116205664559</v>
@@ -1120,19 +1003,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B21" t="n">
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.57426420260096</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.42231348391513</v>
       </c>
       <c r="F21" t="n">
         <v>1.10856491705557</v>
@@ -1149,19 +1032,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.34086242299795</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.42231348391513</v>
       </c>
       <c r="F22" t="n">
         <v>0.811710759378541</v>
@@ -1178,19 +1061,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B23" t="n">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" t="s">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10.5735797399042</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.1854893908282</v>
       </c>
       <c r="F23" t="n">
         <v>0.131820911627031</v>
@@ -1207,19 +1090,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B24" t="n">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" t="s">
-        <v>64</v>
+        <v>26</v>
+      </c>
+      <c r="D24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.12867898699521</v>
       </c>
       <c r="F24" t="n">
         <v>0.16406103968056</v>
@@ -1236,19 +1119,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B25" t="n">
         <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" t="s">
-        <v>65</v>
+        <v>26</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10.5735797399042</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.09787816563997</v>
       </c>
       <c r="F25" t="n">
         <v>0.112647947831333</v>
